--- a/data/raw/Directorio/Correos.xlsx
+++ b/data/raw/Directorio/Correos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/SGING/data/raw/Directorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{3C65D6A3-0B9A-4848-9FCF-60DD4097AE69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89AB2F05-C4B3-4EA4-AAD4-14C280B067EC}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{3C65D6A3-0B9A-4848-9FCF-60DD4097AE69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A947644-AEDA-45CA-9F73-804F86614318}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8B931899-2940-4B42-B68C-D9684CE40C9A}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="240">
   <si>
     <t>Unidades</t>
   </si>
@@ -767,6 +767,9 @@
   </si>
   <si>
     <t>Jose David Ramirez Pachon</t>
+  </si>
+  <si>
+    <t>mjgarzonm@poligran.edu.co,hperez@poligran.edu.co,hperez@poligran.edu.co,careyess@poligran.edu.co,pabernalr@poligran.edu.co,bavelasquez@poligran.edu.co,lxorjuela@poligran.edu.co,agutierrez@poligran.edu.co,clara@poligran.edu.co,amcortesm@poligran.edu.co,hangranadosg@poligran.edu.co,cahernandezmar@poligran.edu.co,rgelvez@poligran.edu.co,lxisilva@poligran.edu.co,fmlopeza@poligran.edu.co,lgiraldo@poligran.edu.co,aramirezr@poligran.edu.co,acarmona@poligran.edu.co,fegarcia@poligran.edu.co,cgarcial@poligran.edu.co,rgarcia@poligran.edu.co,rosadaza@poligran.edu.co,ipmarin@poligran.edu.co,mcruizg@poligran.edu.co,fjoya@poligran.edu.co,rbaquero@poligran.edu.co,noe.casallas@poligran.edu.co,aromant@poligran.edu.co,lpenaran@poligran.edu.co,megrimal@poligran.edu.co,dcjuradob@poligran.edu.co,wjortiza@poligran.edu.co,lcforeror@poligran.edu.co,jcrivera@poligran.edu.co,lvgonzalez@poligran.edu.co,mejimenez@poligran.edu.co,csancheza@poligran.edu.co,lmcorredor@poligran.edu.co,edurane@poligran.edu.co,mavendano@poligran.edu.co,accarmona@poligran.edu.co,drojasd@poligran.edu.co,jcarlcastro@poligran.edu.co,jcacosta@poligran.edu.co,jurmejiat@poligran.edu.co,janmendozat@poligran.edu.co,iadiaz@poligran.edu.co,dgarcia@poligran.edu.co,hperez@poligran.edu.co,lgiraldo@poligran.edu.co,mtrujilo@poligran.edu.co,jcamagudelo@poligran.edu.co,aleguerrero@poligran.edu.co,micortes@poligran.edu.co,dvelasquez@poligran.edu.co,ccoronel@poligran.edu.co,smsanchezb@poligran.edu.co,dbaquero@poligran.edu.co,dbaquero@poligran.edu.co,jediaz@poligran.edu.co,jdsanchezs@poligran.edu.co,jasarmiento@poligran.edu.co,jdevia@poligran.edu.co,demendez@poligran.edu.co,javerano@poligran.edu.co,gespinel@poligran.edu.co,rrcortes@poligran.edu.co,enino@poligran.edu.co,jfhernandez@poligran.edu.co,dricciul@poligran.edu.co,mtequia@poligran.edu.co,jfhernandez@poligran.edu.co,dricciul@poligran.edu.co,mtequia@poligran.edu.co,licabra@poligran.edu.co,ctovar@poligran.edu.co,nivmorenoj@poligran.edu.co,lbarrera@poligran.edu.co,nanrinconp@poligran.edu.co,nivmorenoj@poligran.edu.co,lbarrera@poligran.edu.co,nanrinconp@poligran.edu.co,licabra@poligran.edu.co,ctovar@poligran.edu.co,ccoronel@poligran.edu.co,ccoronel@poligran.edu.co,cromerob@poligran.edu.co,ceariasp@poligran.edu.co,elrodri@poligran.edu.co,apilonie@poligran.edu.co,galgonzalez@poligran.edu.co,caperezc@poligran.edu.co,jddaramirezp@poligran.edu.co,acorreaf@poligran.edu.co,dguerrerop@poligran.edu.co,ipmarin@poligran.edu.co,lmcuellart@poligran.edu.co,acorreaf@poligran.edu.co,aalarcont@poligran.edu.co,rbreton@poligran.edu.co,aromant@poligran.edu.co,mdpreveron@poligran.edu.co,mhortuag@poligran.edu.co,ysolis@poligran.edu.co</t>
   </si>
 </sst>
 </file>
@@ -1193,7 +1196,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3CE0FF-73E4-4985-B199-FA87822AAB2D}">
-  <dimension ref="A1:D105"/>
+  <dimension ref="A1:D111"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="44.44140625" bestFit="1" customWidth="1"/>
@@ -2670,6 +2673,11 @@
         <v>233</v>
       </c>
     </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D111" t="s">
+        <v>239</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data/raw/Directorio/Correos.xlsx
+++ b/data/raw/Directorio/Correos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/SGING/data/raw/Directorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{3C65D6A3-0B9A-4848-9FCF-60DD4097AE69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A947644-AEDA-45CA-9F73-804F86614318}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{3C65D6A3-0B9A-4848-9FCF-60DD4097AE69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A82905CC-12CD-4D8D-88C7-191137600D10}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8B931899-2940-4B42-B68C-D9684CE40C9A}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="239">
   <si>
     <t>Unidades</t>
   </si>
@@ -767,9 +767,6 @@
   </si>
   <si>
     <t>Jose David Ramirez Pachon</t>
-  </si>
-  <si>
-    <t>mjgarzonm@poligran.edu.co,hperez@poligran.edu.co,hperez@poligran.edu.co,careyess@poligran.edu.co,pabernalr@poligran.edu.co,bavelasquez@poligran.edu.co,lxorjuela@poligran.edu.co,agutierrez@poligran.edu.co,clara@poligran.edu.co,amcortesm@poligran.edu.co,hangranadosg@poligran.edu.co,cahernandezmar@poligran.edu.co,rgelvez@poligran.edu.co,lxisilva@poligran.edu.co,fmlopeza@poligran.edu.co,lgiraldo@poligran.edu.co,aramirezr@poligran.edu.co,acarmona@poligran.edu.co,fegarcia@poligran.edu.co,cgarcial@poligran.edu.co,rgarcia@poligran.edu.co,rosadaza@poligran.edu.co,ipmarin@poligran.edu.co,mcruizg@poligran.edu.co,fjoya@poligran.edu.co,rbaquero@poligran.edu.co,noe.casallas@poligran.edu.co,aromant@poligran.edu.co,lpenaran@poligran.edu.co,megrimal@poligran.edu.co,dcjuradob@poligran.edu.co,wjortiza@poligran.edu.co,lcforeror@poligran.edu.co,jcrivera@poligran.edu.co,lvgonzalez@poligran.edu.co,mejimenez@poligran.edu.co,csancheza@poligran.edu.co,lmcorredor@poligran.edu.co,edurane@poligran.edu.co,mavendano@poligran.edu.co,accarmona@poligran.edu.co,drojasd@poligran.edu.co,jcarlcastro@poligran.edu.co,jcacosta@poligran.edu.co,jurmejiat@poligran.edu.co,janmendozat@poligran.edu.co,iadiaz@poligran.edu.co,dgarcia@poligran.edu.co,hperez@poligran.edu.co,lgiraldo@poligran.edu.co,mtrujilo@poligran.edu.co,jcamagudelo@poligran.edu.co,aleguerrero@poligran.edu.co,micortes@poligran.edu.co,dvelasquez@poligran.edu.co,ccoronel@poligran.edu.co,smsanchezb@poligran.edu.co,dbaquero@poligran.edu.co,dbaquero@poligran.edu.co,jediaz@poligran.edu.co,jdsanchezs@poligran.edu.co,jasarmiento@poligran.edu.co,jdevia@poligran.edu.co,demendez@poligran.edu.co,javerano@poligran.edu.co,gespinel@poligran.edu.co,rrcortes@poligran.edu.co,enino@poligran.edu.co,jfhernandez@poligran.edu.co,dricciul@poligran.edu.co,mtequia@poligran.edu.co,jfhernandez@poligran.edu.co,dricciul@poligran.edu.co,mtequia@poligran.edu.co,licabra@poligran.edu.co,ctovar@poligran.edu.co,nivmorenoj@poligran.edu.co,lbarrera@poligran.edu.co,nanrinconp@poligran.edu.co,nivmorenoj@poligran.edu.co,lbarrera@poligran.edu.co,nanrinconp@poligran.edu.co,licabra@poligran.edu.co,ctovar@poligran.edu.co,ccoronel@poligran.edu.co,ccoronel@poligran.edu.co,cromerob@poligran.edu.co,ceariasp@poligran.edu.co,elrodri@poligran.edu.co,apilonie@poligran.edu.co,galgonzalez@poligran.edu.co,caperezc@poligran.edu.co,jddaramirezp@poligran.edu.co,acorreaf@poligran.edu.co,dguerrerop@poligran.edu.co,ipmarin@poligran.edu.co,lmcuellart@poligran.edu.co,acorreaf@poligran.edu.co,aalarcont@poligran.edu.co,rbreton@poligran.edu.co,aromant@poligran.edu.co,mdpreveron@poligran.edu.co,mhortuag@poligran.edu.co,ysolis@poligran.edu.co</t>
   </si>
 </sst>
 </file>
@@ -1196,7 +1193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3CE0FF-73E4-4985-B199-FA87822AAB2D}">
-  <dimension ref="A1:D111"/>
+  <dimension ref="A1:D105"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="44.44140625" bestFit="1" customWidth="1"/>
@@ -2673,11 +2670,6 @@
         <v>233</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D111" t="s">
-        <v>239</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
